--- a/data/trans_camb/IP11-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 2,19</t>
+          <t>-7,94; 2,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 1,1</t>
+          <t>-9,4; 1,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -1,76</t>
+          <t>-10,93; -2,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 8,01</t>
+          <t>-3,23; 8,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 3,04</t>
+          <t>-6,89; 3,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,7; -3,49</t>
+          <t>-11,75; -3,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 3,38</t>
+          <t>-4,01; 3,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 0,44</t>
+          <t>-6,43; 0,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,97; -3,77</t>
+          <t>-9,69; -3,46</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,04; 34,13</t>
+          <t>-66,64; 40,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-77,55; 26,75</t>
+          <t>-79,09; 22,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,01; -13,05</t>
+          <t>-91,02; -24,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,49; 139,21</t>
+          <t>-30,28; 127,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 49,37</t>
+          <t>-60,26; 60,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,11; -43,56</t>
+          <t>-96,03; -42,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 47,21</t>
+          <t>-37,42; 50,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,71; 7,59</t>
+          <t>-60,01; 11,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-88,43; -46,09</t>
+          <t>-87,61; -46,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,02</t>
+          <t>2,98; 10,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,56</t>
+          <t>-2,5; 3,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,48</t>
+          <t>-4,06; 1,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 6,49</t>
+          <t>-1,75; 6,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 2,08</t>
+          <t>-5,36; 2,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; -0,81</t>
+          <t>-7,45; -0,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,4</t>
+          <t>1,41; 7,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,71</t>
+          <t>-2,86; 1,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -0,77</t>
+          <t>-4,9; -0,59</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,46; 499,15</t>
+          <t>48,19; 509,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,7; 161,13</t>
+          <t>-51,51; 177,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,41; 84,34</t>
+          <t>-78,8; 91,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 143,28</t>
+          <t>-22,33; 139,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 51,25</t>
+          <t>-64,26; 46,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,38; -9,62</t>
+          <t>-87,73; -8,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,31; 180,79</t>
+          <t>22,7; 178,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 44,38</t>
+          <t>-45,65; 45,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,34; -14,3</t>
+          <t>-77,33; -10,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,46</t>
+          <t>-3,0; 4,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,3</t>
+          <t>-5,03; 1,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 2,55</t>
+          <t>-5,02; 2,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 10,21</t>
+          <t>-0,34; 10,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 2,61</t>
+          <t>-5,68; 2,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 2,76</t>
+          <t>-5,82; 2,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 6,38</t>
+          <t>-0,17; 6,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 0,83</t>
+          <t>-4,33; 0,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,36</t>
+          <t>-4,32; 1,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 216,59</t>
+          <t>-50,61; 190,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,14; 72,11</t>
+          <t>-77,83; 69,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,13; 91,49</t>
+          <t>-71,89; 106,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 276,22</t>
+          <t>-5,5; 288,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,61; 78,81</t>
+          <t>-67,74; 74,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 70,62</t>
+          <t>-73,63; 81,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 163,26</t>
+          <t>-3,81; 160,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,73; 24,11</t>
+          <t>-60,48; 32,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,14; 38,08</t>
+          <t>-61,73; 35,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,42</t>
+          <t>-2,25; 5,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -0,28</t>
+          <t>-5,87; -0,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,01</t>
+          <t>-5,76; -0,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 8,71</t>
+          <t>0,19; 8,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 4,49</t>
+          <t>-2,79; 4,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,97</t>
+          <t>-4,35; 2,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,81</t>
+          <t>0,25; 5,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,19</t>
+          <t>-3,6; 1,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,5</t>
+          <t>-3,93; 0,35</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 197,04</t>
+          <t>-39,29; 196,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-93,23; 4,64</t>
+          <t>-92,7; 29,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,63; 22,58</t>
+          <t>-91,23; 12,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 233,61</t>
+          <t>-3,65; 240,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 130,7</t>
+          <t>-44,34; 119,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,51; 100,97</t>
+          <t>-64,93; 94,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 163,5</t>
+          <t>0,02; 149,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-57,96; 36,91</t>
+          <t>-58,28; 33,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,68; 15,46</t>
+          <t>-68,5; 16,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,07</t>
+          <t>0,04; 4,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,17</t>
+          <t>-3,55; -0,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -1,01</t>
+          <t>-4,38; -0,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,69</t>
+          <t>0,93; 5,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,02</t>
+          <t>-2,93; 1,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -1,38</t>
+          <t>-5,04; -1,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,21</t>
+          <t>1,17; 4,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -0,09</t>
+          <t>-2,75; -0,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -1,59</t>
+          <t>-4,22; -1,73</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 95,65</t>
+          <t>0,4; 96,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -3,57</t>
+          <t>-57,75; 0,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,13; -21,66</t>
+          <t>-70,73; -19,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,16; 100,17</t>
+          <t>11,43; 101,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 17,91</t>
+          <t>-40,04; 20,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,76; -21,63</t>
+          <t>-68,31; -24,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,59; 79,9</t>
+          <t>17,12; 83,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,63; -1,56</t>
+          <t>-41,9; 0,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-63,84; -31,02</t>
+          <t>-64,81; -33,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP11-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 2,48</t>
+          <t>-8,35; 2,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 1,19</t>
+          <t>-9,07; 0,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,93; -2,05</t>
+          <t>-11,38; -1,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 8,08</t>
+          <t>-3,27; 7,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 3,26</t>
+          <t>-7,01; 3,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -3,27</t>
+          <t>-11,23; -3,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 3,45</t>
+          <t>-4,39; 3,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 0,77</t>
+          <t>-6,46; 0,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -3,46</t>
+          <t>-10,16; -3,73</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,64; 40,78</t>
+          <t>-66,8; 48,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-79,09; 22,64</t>
+          <t>-74,12; 16,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-91,02; -24,73</t>
+          <t>-89,69; -13,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 127,09</t>
+          <t>-31,47; 120,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,26; 60,37</t>
+          <t>-64,85; 65,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-96,03; -42,74</t>
+          <t>-95,24; -37,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 50,25</t>
+          <t>-40,11; 47,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,01; 11,96</t>
+          <t>-59,21; 15,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,61; -46,12</t>
+          <t>-89,01; -49,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,94</t>
+          <t>2,5; 10,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,77</t>
+          <t>-2,05; 3,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,41</t>
+          <t>-3,96; 1,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 6,51</t>
+          <t>-1,6; 6,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 2,07</t>
+          <t>-5,1; 1,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; -0,83</t>
+          <t>-7,26; -1,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,16</t>
+          <t>1,63; 7,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,81</t>
+          <t>-2,6; 1,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -0,59</t>
+          <t>-4,89; -0,81</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,19; 509,95</t>
+          <t>46,71; 471,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,51; 177,64</t>
+          <t>-45,65; 193,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,8; 91,34</t>
+          <t>-79,11; 112,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 139,43</t>
+          <t>-23,14; 130,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,26; 46,74</t>
+          <t>-61,7; 44,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,73; -8,38</t>
+          <t>-86,26; -12,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,7; 178,31</t>
+          <t>22,71; 181,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 45,46</t>
+          <t>-43,28; 47,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,33; -10,41</t>
+          <t>-79,57; -15,46</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-1,13</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-1,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 4,99</t>
+          <t>-2,69; 4,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,56</t>
+          <t>-5,63; 1,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 2,53</t>
+          <t>-5,16; 2,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 10,27</t>
+          <t>-0,03; 9,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 2,82</t>
+          <t>-5,05; 2,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 2,91</t>
+          <t>-5,25; 3,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 6,3</t>
+          <t>-0,2; 6,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,98</t>
+          <t>-4,32; 1,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 1,44</t>
+          <t>-3,97; 1,76</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-25,01%</t>
+          <t>-24,69%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-25,37%</t>
+          <t>-25,2%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,61; 190,49</t>
+          <t>-47,59; 200,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,83; 69,61</t>
+          <t>-80,29; 62,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,89; 106,36</t>
+          <t>-74,51; 110,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 288,98</t>
+          <t>-4,53; 255,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,74; 74,87</t>
+          <t>-63,9; 80,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,63; 81,24</t>
+          <t>-69,88; 81,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 160,98</t>
+          <t>-6,61; 169,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-60,48; 32,87</t>
+          <t>-61,37; 29,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 35,84</t>
+          <t>-59,13; 49,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 5,39</t>
+          <t>-2,07; 5,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -0,18</t>
+          <t>-5,72; 0,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,76; -0,2</t>
+          <t>-5,65; -0,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,54</t>
+          <t>0,14; 8,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 4,12</t>
+          <t>-2,91; 4,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,9</t>
+          <t>-4,51; 2,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,59</t>
+          <t>0,34; 5,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,12</t>
+          <t>-3,47; 1,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 0,35</t>
+          <t>-4,26; 0,35</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,29; 196,75</t>
+          <t>-37,08; 199,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-92,7; 29,4</t>
+          <t>-92,38; 24,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,23; 12,38</t>
+          <t>-91,49; 15,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 240,79</t>
+          <t>-5,34; 263,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 119,79</t>
+          <t>-44,97; 131,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,93; 94,92</t>
+          <t>-69,18; 87,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,02; 149,94</t>
+          <t>3,53; 168,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 33,95</t>
+          <t>-58,78; 32,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,5; 16,69</t>
+          <t>-70,53; 15,08</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,61</t>
+          <t>-2,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,16</t>
+          <t>0,04; 4,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,04</t>
+          <t>-3,59; -0,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,85</t>
+          <t>-4,37; -0,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,68</t>
+          <t>1,09; 5,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,11</t>
+          <t>-3,05; 0,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -1,29</t>
+          <t>-5,14; -1,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,3</t>
+          <t>1,05; 4,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,02</t>
+          <t>-2,61; -0,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -1,73</t>
+          <t>-4,31; -1,73</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-50,3%</t>
+          <t>-50,24%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-50,48%</t>
+          <t>-50,45%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,4; 96,79</t>
+          <t>0,09; 101,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,75; 0,56</t>
+          <t>-57,18; 1,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,73; -19,59</t>
+          <t>-70,82; -21,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,43; 101,8</t>
+          <t>14,44; 101,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 20,92</t>
+          <t>-40,33; 15,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,31; -24,88</t>
+          <t>-68,33; -23,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,12; 83,9</t>
+          <t>14,46; 78,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 0,14</t>
+          <t>-41,54; -1,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-64,81; -33,97</t>
+          <t>-64,94; -32,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP11-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,89</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,06</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,88</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,01</t>
+          <t>-6,28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,7</t>
+          <t>-6,58</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 2,83</t>
+          <t>-3,75; 8,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 0,8</t>
+          <t>-7,06; 3,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,38; -1,78</t>
+          <t>-11,49; -3,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 7,83</t>
+          <t>-7,96; 2,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 3,36</t>
+          <t>-9,37; 1,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; -3,33</t>
+          <t>-11,26; -1,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 3,31</t>
+          <t>-4,41; 3,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 0,79</t>
+          <t>-7,0; 0,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -3,73</t>
+          <t>-9,91; -3,66</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-21,73%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-79,69%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-29,92%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-43,68%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-67,91%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,34%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-21,73%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-81,0%</t>
+          <t>-67,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-74,85%</t>
+          <t>-73,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 48,39</t>
+          <t>-36,49; 139,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,12; 16,48</t>
+          <t>-61,48; 49,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,69; -13,39</t>
+          <t>-94,77; -38,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 120,57</t>
+          <t>-66,04; 34,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,85; 65,52</t>
+          <t>-77,55; 26,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,24; -37,72</t>
+          <t>-88,82; -9,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 47,53</t>
+          <t>-41,04; 47,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,21; 15,24</t>
+          <t>-63,71; 7,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-89,01; -49,54</t>
+          <t>-88,24; -42,64</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,51</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,01</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,78</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,72</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,25</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,75</t>
+          <t>-2,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 10,85</t>
+          <t>-1,92; 6,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,75</t>
+          <t>-5,11; 2,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,67</t>
+          <t>-7,31; -0,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 6,28</t>
+          <t>3,2; 11,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 1,91</t>
+          <t>-2,13; 3,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; -1,2</t>
+          <t>-3,84; 1,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,31</t>
+          <t>1,86; 7,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,88</t>
+          <t>-3,07; 1,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -0,81</t>
+          <t>-4,88; -0,61</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34,83%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-23,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-62,02%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>187,71%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>20,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-34,1%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34,83%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-23,31%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-64,04%</t>
+          <t>-30,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-53,93%</t>
+          <t>-51,41%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,71; 471,03</t>
+          <t>-21,82; 143,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 193,48</t>
+          <t>-61,07; 51,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,11; 112,28</t>
+          <t>-85,97; -4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 130,05</t>
+          <t>53,46; 499,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,7; 44,57</t>
+          <t>-47,7; 161,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,26; -12,48</t>
+          <t>-79,77; 88,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,71; 181,64</t>
+          <t>26,31; 180,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,28; 47,58</t>
+          <t>-46,61; 44,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-79,57; -15,46</t>
+          <t>-76,58; -11,95</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,99</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,21</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,49</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,73</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,99</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,21</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>-0,52</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3,0</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>-1,47</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-1,47</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>-1,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 4,92</t>
+          <t>0,06; 10,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 1,47</t>
+          <t>-5,32; 2,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 2,41</t>
+          <t>-5,75; 2,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 9,95</t>
+          <t>-3,2; 5,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 2,78</t>
+          <t>-5,32; 1,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 3,26</t>
+          <t>-4,89; 3,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 6,23</t>
+          <t>-0,24; 6,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 1,08</t>
+          <t>-4,07; 0,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,76</t>
+          <t>-4,04; 1,79</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>83,89%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-20,33%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-25,06%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>19,36%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-37,71%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-24,69%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-20,33%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,72%</t>
+          <t>-11,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-25,2%</t>
+          <t>-19,34%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,59; 200,53</t>
+          <t>-2,08; 276,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,29; 62,08</t>
+          <t>-63,61; 78,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,51; 110,59</t>
+          <t>-74,12; 67,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 255,19</t>
+          <t>-50,82; 216,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,9; 80,98</t>
+          <t>-78,14; 72,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,88; 81,38</t>
+          <t>-71,6; 130,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 169,07</t>
+          <t>-6,25; 163,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 29,07</t>
+          <t>-58,73; 24,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,13; 49,91</t>
+          <t>-58,7; 48,12</t>
         </is>
       </c>
     </row>
@@ -1272,34 +1272,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,58</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,73</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-2,88</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-2,78</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,24</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,58</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,97</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-1,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,64</t>
+          <t>0,06; 8,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 0,01</t>
+          <t>-2,93; 4,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,65; -0,03</t>
+          <t>-4,37; 2,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 8,94</t>
+          <t>-1,91; 5,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,45</t>
+          <t>-5,92; -0,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 2,77</t>
+          <t>-5,85; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,93</t>
+          <t>0,13; 5,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,12</t>
+          <t>-3,57; 1,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,35</t>
+          <t>-4,01; 0,37</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>82,4%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11,27%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-22,54%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>39,95%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-66,75%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-64,47%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>82,4%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-19,11%</t>
+          <t>-64,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-38,74%</t>
+          <t>-41,44%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 199,52</t>
+          <t>-2,33; 233,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-92,38; 24,41</t>
+          <t>-44,72; 130,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,49; 15,34</t>
+          <t>-66,95; 89,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 263,35</t>
+          <t>-35,76; 197,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 131,79</t>
+          <t>-93,23; 4,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,18; 87,53</t>
+          <t>-92,2; 23,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,53; 168,56</t>
+          <t>1,53; 163,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,78; 32,15</t>
+          <t>-57,96; 36,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,53; 15,08</t>
+          <t>-71,1; 12,23</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,96</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-3,26</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,09</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,86</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,6</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,33</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,28</t>
+          <t>-2,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,94</t>
+          <t>-2,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,37</t>
+          <t>1,08; 5,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,04</t>
+          <t>-2,94; 1,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; -0,96</t>
+          <t>-5,24; -1,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,68</t>
+          <t>-0,05; 4,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,91</t>
+          <t>-3,79; -0,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -1,33</t>
+          <t>-4,05; -0,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,19</t>
+          <t>1,08; 4,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,07</t>
+          <t>-2,94; -0,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,31; -1,73</t>
+          <t>-4,18; -1,53</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>51,76%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-14,92%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-50,61%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>40,31%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-35,79%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-50,24%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>51,76%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-14,92%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-50,94%</t>
+          <t>-47,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-50,45%</t>
+          <t>-49,07%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,09; 101,47</t>
+          <t>13,16; 100,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,18; 1,69</t>
+          <t>-39,9; 17,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-70,82; -21,23</t>
+          <t>-68,79; -21,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,44; 101,7</t>
+          <t>-1,32; 95,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 15,84</t>
+          <t>-60,67; -3,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,33; -23,97</t>
+          <t>-67,11; -14,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,46; 78,68</t>
+          <t>15,59; 79,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,54; -1,14</t>
+          <t>-43,63; -1,56</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-64,94; -32,89</t>
+          <t>-63,21; -30,32</t>
         </is>
       </c>
     </row>
